--- a/pipeline/credit_rating/output/fiinratings_xhtn_20261027.xlsx
+++ b/pipeline/credit_rating/output/fiinratings_xhtn_20261027.xlsx
@@ -553,7 +553,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O2" s="1" t="n">
@@ -624,7 +624,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O3" s="1" t="n">
@@ -691,7 +691,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O4" s="1" t="n">
@@ -762,7 +762,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O5" s="1" t="n">
@@ -833,7 +833,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O6" s="1" t="n">
@@ -896,7 +896,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O7" s="1" t="n">
@@ -967,7 +967,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O8" s="1" t="n">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O9" s="1" t="n">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O10" s="1" t="n">
@@ -1172,7 +1172,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O11" s="1" t="n">
@@ -1235,7 +1235,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O12" s="1" t="n">
@@ -1302,7 +1302,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O13" s="1" t="n">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O14" s="1" t="n">
@@ -1440,7 +1440,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O15" s="1" t="n">
@@ -1503,7 +1503,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O16" s="1" t="n">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O17" s="1" t="n">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O18" s="1" t="n">
@@ -1716,7 +1716,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O19" s="1" t="n">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O20" s="1" t="n">
@@ -1846,7 +1846,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O21" s="1" t="n">
@@ -1909,7 +1909,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O22" s="1" t="n">
@@ -1972,7 +1972,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O23" s="1" t="n">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O24" s="1" t="n">
@@ -2098,7 +2098,7 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O25" s="1" t="n">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O26" s="1" t="n">
@@ -2228,7 +2228,7 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O27" s="1" t="n">
@@ -2295,7 +2295,7 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O28" s="1" t="n">
@@ -2358,7 +2358,7 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O29" s="1" t="n">
@@ -2425,7 +2425,7 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O30" s="1" t="n">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O31" s="1" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O32" s="1" t="n">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O33" s="1" t="n">
@@ -2685,7 +2685,7 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O34" s="1" t="n">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O35" s="1" t="n">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O36" s="1" t="n">
@@ -2874,7 +2874,7 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O37" s="1" t="n">
@@ -2941,7 +2941,7 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O38" s="1" t="n">
@@ -3004,7 +3004,7 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O39" s="1" t="n">
@@ -3071,7 +3071,7 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O40" s="1" t="n">
@@ -3134,7 +3134,7 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O41" s="1" t="n">
@@ -3197,7 +3197,7 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O42" s="1" t="n">
@@ -3260,7 +3260,7 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O43" s="1" t="n">
@@ -3327,7 +3327,7 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O44" s="1" t="n">
@@ -3394,7 +3394,7 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O45" s="1" t="n">
@@ -3457,7 +3457,7 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O46" s="1" t="n">
@@ -3520,7 +3520,7 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O47" s="1" t="n">
@@ -3583,7 +3583,7 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O48" s="1" t="n">
@@ -3650,7 +3650,7 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O49" s="1" t="n">
@@ -3713,7 +3713,7 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O50" s="1" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O51" s="1" t="n">
@@ -3839,7 +3839,7 @@
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O52" s="1" t="n">
@@ -3902,7 +3902,7 @@
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O53" s="1" t="n">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O54" s="1" t="n">
@@ -4028,7 +4028,7 @@
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O55" s="1" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O56" s="1" t="n">
@@ -4158,7 +4158,7 @@
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O57" s="1" t="n">
@@ -4221,7 +4221,7 @@
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O58" s="1" t="n">
@@ -4288,7 +4288,7 @@
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O59" s="1" t="n">
@@ -4351,7 +4351,7 @@
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O60" s="1" t="n">
@@ -4414,7 +4414,7 @@
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O61" s="1" t="n">
@@ -4477,7 +4477,7 @@
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O62" s="1" t="n">
@@ -4540,7 +4540,7 @@
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O63" s="1" t="n">
@@ -4603,7 +4603,7 @@
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O64" s="1" t="n">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O65" s="1" t="n">
@@ -4729,7 +4729,7 @@
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O66" s="1" t="n">
@@ -4792,7 +4792,7 @@
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O67" s="1" t="n">
@@ -4859,7 +4859,7 @@
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O68" s="1" t="n">
@@ -4922,7 +4922,7 @@
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O69" s="1" t="n">
@@ -4985,7 +4985,7 @@
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O70" s="1" t="n">
@@ -5052,7 +5052,7 @@
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O71" s="1" t="n">
@@ -5115,7 +5115,7 @@
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O72" s="1" t="n">
@@ -5182,7 +5182,7 @@
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O73" s="1" t="n">
@@ -5245,7 +5245,7 @@
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O74" s="1" t="n">
@@ -5308,7 +5308,7 @@
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O75" s="1" t="n">
@@ -5371,7 +5371,7 @@
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O76" s="1" t="n">
@@ -5434,7 +5434,7 @@
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O77" s="1" t="n">
@@ -5497,7 +5497,7 @@
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O78" s="1" t="n">
@@ -5564,7 +5564,7 @@
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O79" s="1" t="n">
@@ -5627,7 +5627,7 @@
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O80" s="1" t="n">
@@ -5690,7 +5690,7 @@
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O81" s="1" t="n">
@@ -5753,7 +5753,7 @@
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O82" s="1" t="n">
@@ -5816,7 +5816,7 @@
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O83" s="1" t="n">
@@ -5879,7 +5879,7 @@
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O84" s="1" t="n">
@@ -5942,7 +5942,7 @@
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O85" s="1" t="n">
@@ -6009,7 +6009,7 @@
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O86" s="1" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O87" s="1" t="n">
@@ -6135,7 +6135,7 @@
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O88" s="1" t="n">
@@ -6198,7 +6198,7 @@
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O89" s="1" t="n">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O90" s="1" t="n">
@@ -6324,7 +6324,7 @@
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O91" s="1" t="n">
@@ -6387,7 +6387,7 @@
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O92" s="1" t="n">
@@ -6450,7 +6450,7 @@
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O93" s="1" t="n">
@@ -6513,7 +6513,7 @@
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O94" s="1" t="n">
@@ -6576,7 +6576,7 @@
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O95" s="1" t="n">
@@ -6639,7 +6639,7 @@
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O96" s="1" t="n">
@@ -6702,7 +6702,7 @@
       </c>
       <c r="N97" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O97" s="1" t="n">
@@ -6765,7 +6765,7 @@
       </c>
       <c r="N98" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O98" s="1" t="n">
@@ -6828,7 +6828,7 @@
       </c>
       <c r="N99" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O99" s="1" t="n">
@@ -6891,7 +6891,7 @@
       </c>
       <c r="N100" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O100" s="1" t="n">
@@ -6958,7 +6958,7 @@
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O101" s="1" t="n">
@@ -7021,7 +7021,7 @@
       </c>
       <c r="N102" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O102" s="1" t="n">
@@ -7084,7 +7084,7 @@
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O103" s="1" t="n">
@@ -7151,7 +7151,7 @@
       </c>
       <c r="N104" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O104" s="1" t="n">
@@ -7214,7 +7214,7 @@
       </c>
       <c r="N105" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O105" s="1" t="n">
@@ -7277,7 +7277,7 @@
       </c>
       <c r="N106" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O106" s="1" t="n">
@@ -7340,7 +7340,7 @@
       </c>
       <c r="N107" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O107" s="1" t="n">
@@ -7407,7 +7407,7 @@
       </c>
       <c r="N108" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O108" s="1" t="n">
@@ -7470,7 +7470,7 @@
       </c>
       <c r="N109" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O109" s="1" t="n">
@@ -7533,7 +7533,7 @@
       </c>
       <c r="N110" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O110" s="1" t="n">
@@ -7596,7 +7596,7 @@
       </c>
       <c r="N111" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O111" s="1" t="n">
@@ -7659,7 +7659,7 @@
       </c>
       <c r="N112" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O112" s="1" t="n">
@@ -7722,7 +7722,7 @@
       </c>
       <c r="N113" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O113" s="1" t="n">
@@ -7785,7 +7785,7 @@
       </c>
       <c r="N114" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O114" s="1" t="n">
@@ -7852,7 +7852,7 @@
       </c>
       <c r="N115" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O115" s="1" t="n">
@@ -7915,7 +7915,7 @@
       </c>
       <c r="N116" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O116" s="1" t="n">
@@ -7978,7 +7978,7 @@
       </c>
       <c r="N117" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O117" s="1" t="n">
@@ -8041,7 +8041,7 @@
       </c>
       <c r="N118" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O118" s="1" t="n">
@@ -8104,7 +8104,7 @@
       </c>
       <c r="N119" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O119" s="1" t="n">
@@ -8167,7 +8167,7 @@
       </c>
       <c r="N120" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O120" s="1" t="n">
@@ -8230,7 +8230,7 @@
       </c>
       <c r="N121" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O121" s="1" t="n">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="N122" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O122" s="1" t="n">
@@ -8356,7 +8356,7 @@
       </c>
       <c r="N123" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O123" s="1" t="n">
@@ -8419,7 +8419,7 @@
       </c>
       <c r="N124" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O124" s="1" t="n">
@@ -8482,7 +8482,7 @@
       </c>
       <c r="N125" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O125" s="1" t="n">
@@ -8545,7 +8545,7 @@
       </c>
       <c r="N126" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O126" s="1" t="n">
@@ -8608,7 +8608,7 @@
       </c>
       <c r="N127" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O127" s="1" t="n">
@@ -8671,7 +8671,7 @@
       </c>
       <c r="N128" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O128" s="1" t="n">
@@ -8734,7 +8734,7 @@
       </c>
       <c r="N129" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O129" s="1" t="n">
@@ -8797,7 +8797,7 @@
       </c>
       <c r="N130" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O130" s="1" t="n">
@@ -8860,7 +8860,7 @@
       </c>
       <c r="N131" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O131" s="1" t="n">
@@ -8923,7 +8923,7 @@
       </c>
       <c r="N132" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O132" s="1" t="n">
@@ -8986,7 +8986,7 @@
       </c>
       <c r="N133" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O133" s="1" t="n">
@@ -9053,7 +9053,7 @@
       </c>
       <c r="N134" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O134" s="1" t="n">
@@ -9116,7 +9116,7 @@
       </c>
       <c r="N135" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O135" s="1" t="n">
@@ -9183,7 +9183,7 @@
       </c>
       <c r="N136" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O136" s="1" t="n">
@@ -9246,7 +9246,7 @@
       </c>
       <c r="N137" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O137" s="1" t="n">
@@ -9309,7 +9309,7 @@
       </c>
       <c r="N138" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O138" s="1" t="n">
@@ -9372,7 +9372,7 @@
       </c>
       <c r="N139" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O139" s="1" t="n">
@@ -9439,7 +9439,7 @@
       </c>
       <c r="N140" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O140" s="1" t="n">
@@ -9502,7 +9502,7 @@
       </c>
       <c r="N141" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O141" s="1" t="n">
@@ -9565,7 +9565,7 @@
       </c>
       <c r="N142" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O142" s="1" t="n">
@@ -9628,7 +9628,7 @@
       </c>
       <c r="N143" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O143" s="1" t="n">
@@ -9691,7 +9691,7 @@
       </c>
       <c r="N144" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O144" s="1" t="n">
@@ -9754,7 +9754,7 @@
       </c>
       <c r="N145" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O145" s="1" t="n">
@@ -9817,7 +9817,7 @@
       </c>
       <c r="N146" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O146" s="1" t="n">
@@ -9880,7 +9880,7 @@
       </c>
       <c r="N147" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O147" s="1" t="n">
@@ -9943,7 +9943,7 @@
       </c>
       <c r="N148" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O148" s="1" t="n">
@@ -10006,7 +10006,7 @@
       </c>
       <c r="N149" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O149" s="1" t="n">
@@ -10069,7 +10069,7 @@
       </c>
       <c r="N150" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O150" s="1" t="n">
@@ -10132,7 +10132,7 @@
       </c>
       <c r="N151" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O151" s="1" t="n">
@@ -10195,7 +10195,7 @@
       </c>
       <c r="N152" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O152" s="1" t="n">
@@ -10258,7 +10258,7 @@
       </c>
       <c r="N153" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O153" s="1" t="n">
@@ -10321,7 +10321,7 @@
       </c>
       <c r="N154" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O154" s="1" t="n">
@@ -10384,7 +10384,7 @@
       </c>
       <c r="N155" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O155" s="1" t="n">
@@ -10447,7 +10447,7 @@
       </c>
       <c r="N156" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O156" s="1" t="n">
@@ -10510,7 +10510,7 @@
       </c>
       <c r="N157" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O157" s="1" t="n">
@@ -10573,7 +10573,7 @@
       </c>
       <c r="N158" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O158" s="1" t="n">
@@ -10636,7 +10636,7 @@
       </c>
       <c r="N159" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O159" s="1" t="n">
@@ -10699,7 +10699,7 @@
       </c>
       <c r="N160" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O160" s="1" t="n">
@@ -10762,7 +10762,7 @@
       </c>
       <c r="N161" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O161" s="1" t="n">
@@ -10825,7 +10825,7 @@
       </c>
       <c r="N162" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O162" s="1" t="n">
@@ -10888,7 +10888,7 @@
       </c>
       <c r="N163" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O163" s="1" t="n">
@@ -10951,7 +10951,7 @@
       </c>
       <c r="N164" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O164" s="1" t="n">
@@ -11014,7 +11014,7 @@
       </c>
       <c r="N165" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O165" s="1" t="n">
@@ -11077,7 +11077,7 @@
       </c>
       <c r="N166" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O166" s="1" t="n">
@@ -11140,7 +11140,7 @@
       </c>
       <c r="N167" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O167" s="1" t="n">
@@ -11203,7 +11203,7 @@
       </c>
       <c r="N168" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O168" s="1" t="n">
@@ -11266,7 +11266,7 @@
       </c>
       <c r="N169" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O169" s="1" t="n">
@@ -11329,7 +11329,7 @@
       </c>
       <c r="N170" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O170" s="1" t="n">
@@ -11392,7 +11392,7 @@
       </c>
       <c r="N171" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O171" s="1" t="n">
@@ -11455,7 +11455,7 @@
       </c>
       <c r="N172" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O172" s="1" t="n">
@@ -11518,7 +11518,7 @@
       </c>
       <c r="N173" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O173" s="1" t="n">
@@ -11581,7 +11581,7 @@
       </c>
       <c r="N174" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O174" s="1" t="n">
@@ -11644,7 +11644,7 @@
       </c>
       <c r="N175" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O175" s="1" t="n">
@@ -11707,7 +11707,7 @@
       </c>
       <c r="N176" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O176" s="1" t="n">
@@ -11770,7 +11770,7 @@
       </c>
       <c r="N177" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O177" s="1" t="n">
@@ -11833,7 +11833,7 @@
       </c>
       <c r="N178" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O178" s="1" t="n">
@@ -11896,7 +11896,7 @@
       </c>
       <c r="N179" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O179" s="1" t="n">
@@ -11959,7 +11959,7 @@
       </c>
       <c r="N180" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O180" s="1" t="n">
@@ -12022,7 +12022,7 @@
       </c>
       <c r="N181" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O181" s="1" t="n">
@@ -12085,7 +12085,7 @@
       </c>
       <c r="N182" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O182" s="1" t="n">
@@ -12148,7 +12148,7 @@
       </c>
       <c r="N183" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O183" s="1" t="n">
@@ -12211,7 +12211,7 @@
       </c>
       <c r="N184" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O184" s="1" t="n">
@@ -12274,7 +12274,7 @@
       </c>
       <c r="N185" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O185" s="1" t="n">
@@ -12337,7 +12337,7 @@
       </c>
       <c r="N186" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O186" s="1" t="n">
@@ -12400,7 +12400,7 @@
       </c>
       <c r="N187" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O187" s="1" t="n">
@@ -12463,7 +12463,7 @@
       </c>
       <c r="N188" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O188" s="1" t="n">
@@ -12526,7 +12526,7 @@
       </c>
       <c r="N189" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O189" s="1" t="n">
@@ -12589,7 +12589,7 @@
       </c>
       <c r="N190" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O190" s="1" t="n">
@@ -12652,7 +12652,7 @@
       </c>
       <c r="N191" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O191" s="1" t="n">
@@ -12715,7 +12715,7 @@
       </c>
       <c r="N192" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O192" s="1" t="n">
@@ -12778,7 +12778,7 @@
       </c>
       <c r="N193" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O193" s="1" t="n">
@@ -12841,7 +12841,7 @@
       </c>
       <c r="N194" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O194" s="1" t="n">
@@ -12904,7 +12904,7 @@
       </c>
       <c r="N195" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O195" s="1" t="n">
@@ -12967,7 +12967,7 @@
       </c>
       <c r="N196" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O196" s="1" t="n">
@@ -13030,7 +13030,7 @@
       </c>
       <c r="N197" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O197" s="1" t="n">
@@ -13093,7 +13093,7 @@
       </c>
       <c r="N198" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O198" s="1" t="n">
@@ -13156,7 +13156,7 @@
       </c>
       <c r="N199" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O199" s="1" t="n">
@@ -13219,7 +13219,7 @@
       </c>
       <c r="N200" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O200" s="1" t="n">
@@ -13282,7 +13282,7 @@
       </c>
       <c r="N201" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O201" s="1" t="n">
@@ -13345,7 +13345,7 @@
       </c>
       <c r="N202" t="inlineStr">
         <is>
-          <t>2026-10-27 02:33:53</t>
+          <t>2026-10-27 02:39:41</t>
         </is>
       </c>
       <c r="O202" s="1" t="n">

--- a/pipeline/credit_rating/output/fiinratings_xhtn_20261027.xlsx
+++ b/pipeline/credit_rating/output/fiinratings_xhtn_20261027.xlsx
@@ -553,7 +553,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O2" s="1" t="n">
@@ -624,7 +624,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O3" s="1" t="n">
@@ -691,7 +691,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O4" s="1" t="n">
@@ -762,7 +762,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O5" s="1" t="n">
@@ -833,7 +833,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O6" s="1" t="n">
@@ -896,7 +896,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O7" s="1" t="n">
@@ -967,7 +967,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O8" s="1" t="n">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O9" s="1" t="n">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O10" s="1" t="n">
@@ -1172,7 +1172,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O11" s="1" t="n">
@@ -1235,7 +1235,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O12" s="1" t="n">
@@ -1302,7 +1302,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O13" s="1" t="n">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O14" s="1" t="n">
@@ -1440,7 +1440,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O15" s="1" t="n">
@@ -1503,7 +1503,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O16" s="1" t="n">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O17" s="1" t="n">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O18" s="1" t="n">
@@ -1716,7 +1716,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O19" s="1" t="n">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O20" s="1" t="n">
@@ -1846,7 +1846,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O21" s="1" t="n">
@@ -1909,7 +1909,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O22" s="1" t="n">
@@ -1972,7 +1972,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O23" s="1" t="n">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O24" s="1" t="n">
@@ -2098,7 +2098,7 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O25" s="1" t="n">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O26" s="1" t="n">
@@ -2228,7 +2228,7 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O27" s="1" t="n">
@@ -2295,7 +2295,7 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O28" s="1" t="n">
@@ -2358,7 +2358,7 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O29" s="1" t="n">
@@ -2425,7 +2425,7 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O30" s="1" t="n">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O31" s="1" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O32" s="1" t="n">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O33" s="1" t="n">
@@ -2685,7 +2685,7 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O34" s="1" t="n">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O35" s="1" t="n">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O36" s="1" t="n">
@@ -2874,7 +2874,7 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O37" s="1" t="n">
@@ -2941,7 +2941,7 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O38" s="1" t="n">
@@ -3004,7 +3004,7 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O39" s="1" t="n">
@@ -3071,7 +3071,7 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O40" s="1" t="n">
@@ -3134,7 +3134,7 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O41" s="1" t="n">
@@ -3197,7 +3197,7 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O42" s="1" t="n">
@@ -3260,7 +3260,7 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O43" s="1" t="n">
@@ -3327,7 +3327,7 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O44" s="1" t="n">
@@ -3394,7 +3394,7 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O45" s="1" t="n">
@@ -3457,7 +3457,7 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O46" s="1" t="n">
@@ -3520,7 +3520,7 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O47" s="1" t="n">
@@ -3583,7 +3583,7 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O48" s="1" t="n">
@@ -3650,7 +3650,7 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O49" s="1" t="n">
@@ -3713,7 +3713,7 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O50" s="1" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O51" s="1" t="n">
@@ -3839,7 +3839,7 @@
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O52" s="1" t="n">
@@ -3902,7 +3902,7 @@
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O53" s="1" t="n">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O54" s="1" t="n">
@@ -4028,7 +4028,7 @@
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O55" s="1" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O56" s="1" t="n">
@@ -4158,7 +4158,7 @@
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O57" s="1" t="n">
@@ -4221,7 +4221,7 @@
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O58" s="1" t="n">
@@ -4288,7 +4288,7 @@
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O59" s="1" t="n">
@@ -4351,7 +4351,7 @@
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O60" s="1" t="n">
@@ -4414,7 +4414,7 @@
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O61" s="1" t="n">
@@ -4477,7 +4477,7 @@
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O62" s="1" t="n">
@@ -4540,7 +4540,7 @@
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O63" s="1" t="n">
@@ -4603,7 +4603,7 @@
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O64" s="1" t="n">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O65" s="1" t="n">
@@ -4729,7 +4729,7 @@
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O66" s="1" t="n">
@@ -4792,7 +4792,7 @@
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O67" s="1" t="n">
@@ -4859,7 +4859,7 @@
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O68" s="1" t="n">
@@ -4922,7 +4922,7 @@
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O69" s="1" t="n">
@@ -4985,7 +4985,7 @@
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O70" s="1" t="n">
@@ -5052,7 +5052,7 @@
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O71" s="1" t="n">
@@ -5115,7 +5115,7 @@
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O72" s="1" t="n">
@@ -5182,7 +5182,7 @@
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O73" s="1" t="n">
@@ -5245,7 +5245,7 @@
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O74" s="1" t="n">
@@ -5308,7 +5308,7 @@
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O75" s="1" t="n">
@@ -5371,7 +5371,7 @@
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O76" s="1" t="n">
@@ -5434,7 +5434,7 @@
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O77" s="1" t="n">
@@ -5497,7 +5497,7 @@
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O78" s="1" t="n">
@@ -5564,7 +5564,7 @@
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O79" s="1" t="n">
@@ -5627,7 +5627,7 @@
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O80" s="1" t="n">
@@ -5690,7 +5690,7 @@
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O81" s="1" t="n">
@@ -5753,7 +5753,7 @@
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O82" s="1" t="n">
@@ -5816,7 +5816,7 @@
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O83" s="1" t="n">
@@ -5879,7 +5879,7 @@
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O84" s="1" t="n">
@@ -5942,7 +5942,7 @@
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O85" s="1" t="n">
@@ -6009,7 +6009,7 @@
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O86" s="1" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O87" s="1" t="n">
@@ -6135,7 +6135,7 @@
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O88" s="1" t="n">
@@ -6198,7 +6198,7 @@
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O89" s="1" t="n">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O90" s="1" t="n">
@@ -6324,7 +6324,7 @@
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O91" s="1" t="n">
@@ -6387,7 +6387,7 @@
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O92" s="1" t="n">
@@ -6450,7 +6450,7 @@
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O93" s="1" t="n">
@@ -6513,7 +6513,7 @@
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O94" s="1" t="n">
@@ -6576,7 +6576,7 @@
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O95" s="1" t="n">
@@ -6639,7 +6639,7 @@
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O96" s="1" t="n">
@@ -6702,7 +6702,7 @@
       </c>
       <c r="N97" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O97" s="1" t="n">
@@ -6765,7 +6765,7 @@
       </c>
       <c r="N98" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O98" s="1" t="n">
@@ -6828,7 +6828,7 @@
       </c>
       <c r="N99" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O99" s="1" t="n">
@@ -6891,7 +6891,7 @@
       </c>
       <c r="N100" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O100" s="1" t="n">
@@ -6958,7 +6958,7 @@
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O101" s="1" t="n">
@@ -7021,7 +7021,7 @@
       </c>
       <c r="N102" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O102" s="1" t="n">
@@ -7084,7 +7084,7 @@
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O103" s="1" t="n">
@@ -7151,7 +7151,7 @@
       </c>
       <c r="N104" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O104" s="1" t="n">
@@ -7214,7 +7214,7 @@
       </c>
       <c r="N105" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O105" s="1" t="n">
@@ -7277,7 +7277,7 @@
       </c>
       <c r="N106" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O106" s="1" t="n">
@@ -7340,7 +7340,7 @@
       </c>
       <c r="N107" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O107" s="1" t="n">
@@ -7407,7 +7407,7 @@
       </c>
       <c r="N108" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O108" s="1" t="n">
@@ -7470,7 +7470,7 @@
       </c>
       <c r="N109" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O109" s="1" t="n">
@@ -7533,7 +7533,7 @@
       </c>
       <c r="N110" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O110" s="1" t="n">
@@ -7596,7 +7596,7 @@
       </c>
       <c r="N111" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O111" s="1" t="n">
@@ -7659,7 +7659,7 @@
       </c>
       <c r="N112" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O112" s="1" t="n">
@@ -7722,7 +7722,7 @@
       </c>
       <c r="N113" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O113" s="1" t="n">
@@ -7785,7 +7785,7 @@
       </c>
       <c r="N114" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O114" s="1" t="n">
@@ -7852,7 +7852,7 @@
       </c>
       <c r="N115" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O115" s="1" t="n">
@@ -7915,7 +7915,7 @@
       </c>
       <c r="N116" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O116" s="1" t="n">
@@ -7978,7 +7978,7 @@
       </c>
       <c r="N117" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O117" s="1" t="n">
@@ -8041,7 +8041,7 @@
       </c>
       <c r="N118" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O118" s="1" t="n">
@@ -8104,7 +8104,7 @@
       </c>
       <c r="N119" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O119" s="1" t="n">
@@ -8167,7 +8167,7 @@
       </c>
       <c r="N120" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O120" s="1" t="n">
@@ -8230,7 +8230,7 @@
       </c>
       <c r="N121" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O121" s="1" t="n">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="N122" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O122" s="1" t="n">
@@ -8356,7 +8356,7 @@
       </c>
       <c r="N123" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O123" s="1" t="n">
@@ -8419,7 +8419,7 @@
       </c>
       <c r="N124" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O124" s="1" t="n">
@@ -8482,7 +8482,7 @@
       </c>
       <c r="N125" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O125" s="1" t="n">
@@ -8545,7 +8545,7 @@
       </c>
       <c r="N126" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O126" s="1" t="n">
@@ -8608,7 +8608,7 @@
       </c>
       <c r="N127" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O127" s="1" t="n">
@@ -8671,7 +8671,7 @@
       </c>
       <c r="N128" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O128" s="1" t="n">
@@ -8734,7 +8734,7 @@
       </c>
       <c r="N129" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O129" s="1" t="n">
@@ -8797,7 +8797,7 @@
       </c>
       <c r="N130" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O130" s="1" t="n">
@@ -8860,7 +8860,7 @@
       </c>
       <c r="N131" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O131" s="1" t="n">
@@ -8923,7 +8923,7 @@
       </c>
       <c r="N132" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O132" s="1" t="n">
@@ -8986,7 +8986,7 @@
       </c>
       <c r="N133" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O133" s="1" t="n">
@@ -9053,7 +9053,7 @@
       </c>
       <c r="N134" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O134" s="1" t="n">
@@ -9116,7 +9116,7 @@
       </c>
       <c r="N135" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O135" s="1" t="n">
@@ -9183,7 +9183,7 @@
       </c>
       <c r="N136" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O136" s="1" t="n">
@@ -9246,7 +9246,7 @@
       </c>
       <c r="N137" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O137" s="1" t="n">
@@ -9309,7 +9309,7 @@
       </c>
       <c r="N138" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O138" s="1" t="n">
@@ -9372,7 +9372,7 @@
       </c>
       <c r="N139" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O139" s="1" t="n">
@@ -9439,7 +9439,7 @@
       </c>
       <c r="N140" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O140" s="1" t="n">
@@ -9502,7 +9502,7 @@
       </c>
       <c r="N141" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O141" s="1" t="n">
@@ -9565,7 +9565,7 @@
       </c>
       <c r="N142" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O142" s="1" t="n">
@@ -9628,7 +9628,7 @@
       </c>
       <c r="N143" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O143" s="1" t="n">
@@ -9691,7 +9691,7 @@
       </c>
       <c r="N144" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O144" s="1" t="n">
@@ -9754,7 +9754,7 @@
       </c>
       <c r="N145" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O145" s="1" t="n">
@@ -9817,7 +9817,7 @@
       </c>
       <c r="N146" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O146" s="1" t="n">
@@ -9880,7 +9880,7 @@
       </c>
       <c r="N147" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O147" s="1" t="n">
@@ -9943,7 +9943,7 @@
       </c>
       <c r="N148" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O148" s="1" t="n">
@@ -10006,7 +10006,7 @@
       </c>
       <c r="N149" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O149" s="1" t="n">
@@ -10069,7 +10069,7 @@
       </c>
       <c r="N150" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O150" s="1" t="n">
@@ -10132,7 +10132,7 @@
       </c>
       <c r="N151" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O151" s="1" t="n">
@@ -10195,7 +10195,7 @@
       </c>
       <c r="N152" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O152" s="1" t="n">
@@ -10258,7 +10258,7 @@
       </c>
       <c r="N153" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O153" s="1" t="n">
@@ -10321,7 +10321,7 @@
       </c>
       <c r="N154" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O154" s="1" t="n">
@@ -10384,7 +10384,7 @@
       </c>
       <c r="N155" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O155" s="1" t="n">
@@ -10447,7 +10447,7 @@
       </c>
       <c r="N156" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O156" s="1" t="n">
@@ -10510,7 +10510,7 @@
       </c>
       <c r="N157" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O157" s="1" t="n">
@@ -10573,7 +10573,7 @@
       </c>
       <c r="N158" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O158" s="1" t="n">
@@ -10636,7 +10636,7 @@
       </c>
       <c r="N159" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O159" s="1" t="n">
@@ -10699,7 +10699,7 @@
       </c>
       <c r="N160" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O160" s="1" t="n">
@@ -10762,7 +10762,7 @@
       </c>
       <c r="N161" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O161" s="1" t="n">
@@ -10825,7 +10825,7 @@
       </c>
       <c r="N162" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O162" s="1" t="n">
@@ -10888,7 +10888,7 @@
       </c>
       <c r="N163" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O163" s="1" t="n">
@@ -10951,7 +10951,7 @@
       </c>
       <c r="N164" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O164" s="1" t="n">
@@ -11014,7 +11014,7 @@
       </c>
       <c r="N165" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O165" s="1" t="n">
@@ -11077,7 +11077,7 @@
       </c>
       <c r="N166" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O166" s="1" t="n">
@@ -11140,7 +11140,7 @@
       </c>
       <c r="N167" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O167" s="1" t="n">
@@ -11203,7 +11203,7 @@
       </c>
       <c r="N168" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O168" s="1" t="n">
@@ -11266,7 +11266,7 @@
       </c>
       <c r="N169" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O169" s="1" t="n">
@@ -11329,7 +11329,7 @@
       </c>
       <c r="N170" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O170" s="1" t="n">
@@ -11392,7 +11392,7 @@
       </c>
       <c r="N171" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O171" s="1" t="n">
@@ -11455,7 +11455,7 @@
       </c>
       <c r="N172" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O172" s="1" t="n">
@@ -11518,7 +11518,7 @@
       </c>
       <c r="N173" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O173" s="1" t="n">
@@ -11581,7 +11581,7 @@
       </c>
       <c r="N174" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O174" s="1" t="n">
@@ -11644,7 +11644,7 @@
       </c>
       <c r="N175" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O175" s="1" t="n">
@@ -11707,7 +11707,7 @@
       </c>
       <c r="N176" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O176" s="1" t="n">
@@ -11770,7 +11770,7 @@
       </c>
       <c r="N177" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O177" s="1" t="n">
@@ -11833,7 +11833,7 @@
       </c>
       <c r="N178" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O178" s="1" t="n">
@@ -11896,7 +11896,7 @@
       </c>
       <c r="N179" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O179" s="1" t="n">
@@ -11959,7 +11959,7 @@
       </c>
       <c r="N180" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O180" s="1" t="n">
@@ -12022,7 +12022,7 @@
       </c>
       <c r="N181" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O181" s="1" t="n">
@@ -12085,7 +12085,7 @@
       </c>
       <c r="N182" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O182" s="1" t="n">
@@ -12148,7 +12148,7 @@
       </c>
       <c r="N183" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O183" s="1" t="n">
@@ -12211,7 +12211,7 @@
       </c>
       <c r="N184" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O184" s="1" t="n">
@@ -12274,7 +12274,7 @@
       </c>
       <c r="N185" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O185" s="1" t="n">
@@ -12337,7 +12337,7 @@
       </c>
       <c r="N186" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O186" s="1" t="n">
@@ -12400,7 +12400,7 @@
       </c>
       <c r="N187" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O187" s="1" t="n">
@@ -12463,7 +12463,7 @@
       </c>
       <c r="N188" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O188" s="1" t="n">
@@ -12526,7 +12526,7 @@
       </c>
       <c r="N189" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O189" s="1" t="n">
@@ -12589,7 +12589,7 @@
       </c>
       <c r="N190" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O190" s="1" t="n">
@@ -12652,7 +12652,7 @@
       </c>
       <c r="N191" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O191" s="1" t="n">
@@ -12715,7 +12715,7 @@
       </c>
       <c r="N192" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O192" s="1" t="n">
@@ -12778,7 +12778,7 @@
       </c>
       <c r="N193" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O193" s="1" t="n">
@@ -12841,7 +12841,7 @@
       </c>
       <c r="N194" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O194" s="1" t="n">
@@ -12904,7 +12904,7 @@
       </c>
       <c r="N195" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O195" s="1" t="n">
@@ -12967,7 +12967,7 @@
       </c>
       <c r="N196" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O196" s="1" t="n">
@@ -13030,7 +13030,7 @@
       </c>
       <c r="N197" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O197" s="1" t="n">
@@ -13093,7 +13093,7 @@
       </c>
       <c r="N198" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O198" s="1" t="n">
@@ -13156,7 +13156,7 @@
       </c>
       <c r="N199" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O199" s="1" t="n">
@@ -13219,7 +13219,7 @@
       </c>
       <c r="N200" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O200" s="1" t="n">
@@ -13282,7 +13282,7 @@
       </c>
       <c r="N201" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O201" s="1" t="n">
@@ -13345,7 +13345,7 @@
       </c>
       <c r="N202" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:41</t>
+          <t>2026-10-27 09:18:14</t>
         </is>
       </c>
       <c r="O202" s="1" t="n">

--- a/pipeline/credit_rating/output/fiinratings_xhtn_20261027.xlsx
+++ b/pipeline/credit_rating/output/fiinratings_xhtn_20261027.xlsx
@@ -553,7 +553,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O2" s="1" t="n">
@@ -624,7 +624,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O3" s="1" t="n">
@@ -691,7 +691,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O4" s="1" t="n">
@@ -762,7 +762,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O5" s="1" t="n">
@@ -833,7 +833,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O6" s="1" t="n">
@@ -896,7 +896,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O7" s="1" t="n">
@@ -967,7 +967,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O8" s="1" t="n">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O9" s="1" t="n">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O10" s="1" t="n">
@@ -1172,7 +1172,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O11" s="1" t="n">
@@ -1235,7 +1235,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O12" s="1" t="n">
@@ -1302,7 +1302,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O13" s="1" t="n">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O14" s="1" t="n">
@@ -1440,7 +1440,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O15" s="1" t="n">
@@ -1503,7 +1503,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O16" s="1" t="n">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O17" s="1" t="n">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O18" s="1" t="n">
@@ -1716,7 +1716,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O19" s="1" t="n">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O20" s="1" t="n">
@@ -1846,7 +1846,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O21" s="1" t="n">
@@ -1909,7 +1909,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O22" s="1" t="n">
@@ -1972,7 +1972,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O23" s="1" t="n">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O24" s="1" t="n">
@@ -2098,7 +2098,7 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O25" s="1" t="n">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O26" s="1" t="n">
@@ -2228,7 +2228,7 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O27" s="1" t="n">
@@ -2295,7 +2295,7 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O28" s="1" t="n">
@@ -2358,7 +2358,7 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O29" s="1" t="n">
@@ -2425,7 +2425,7 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O30" s="1" t="n">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O31" s="1" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O32" s="1" t="n">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O33" s="1" t="n">
@@ -2685,7 +2685,7 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O34" s="1" t="n">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O35" s="1" t="n">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O36" s="1" t="n">
@@ -2874,7 +2874,7 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O37" s="1" t="n">
@@ -2941,7 +2941,7 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O38" s="1" t="n">
@@ -3004,7 +3004,7 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O39" s="1" t="n">
@@ -3071,7 +3071,7 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O40" s="1" t="n">
@@ -3134,7 +3134,7 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O41" s="1" t="n">
@@ -3197,7 +3197,7 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O42" s="1" t="n">
@@ -3260,7 +3260,7 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O43" s="1" t="n">
@@ -3327,7 +3327,7 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O44" s="1" t="n">
@@ -3394,7 +3394,7 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O45" s="1" t="n">
@@ -3457,7 +3457,7 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O46" s="1" t="n">
@@ -3520,7 +3520,7 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O47" s="1" t="n">
@@ -3583,7 +3583,7 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O48" s="1" t="n">
@@ -3650,7 +3650,7 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O49" s="1" t="n">
@@ -3713,7 +3713,7 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O50" s="1" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O51" s="1" t="n">
@@ -3839,7 +3839,7 @@
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O52" s="1" t="n">
@@ -3902,7 +3902,7 @@
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O53" s="1" t="n">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O54" s="1" t="n">
@@ -4028,7 +4028,7 @@
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O55" s="1" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O56" s="1" t="n">
@@ -4158,7 +4158,7 @@
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O57" s="1" t="n">
@@ -4221,7 +4221,7 @@
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O58" s="1" t="n">
@@ -4288,7 +4288,7 @@
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O59" s="1" t="n">
@@ -4351,7 +4351,7 @@
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O60" s="1" t="n">
@@ -4414,7 +4414,7 @@
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O61" s="1" t="n">
@@ -4477,7 +4477,7 @@
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O62" s="1" t="n">
@@ -4540,7 +4540,7 @@
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O63" s="1" t="n">
@@ -4603,7 +4603,7 @@
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O64" s="1" t="n">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O65" s="1" t="n">
@@ -4729,7 +4729,7 @@
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O66" s="1" t="n">
@@ -4792,7 +4792,7 @@
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O67" s="1" t="n">
@@ -4859,7 +4859,7 @@
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O68" s="1" t="n">
@@ -4922,7 +4922,7 @@
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O69" s="1" t="n">
@@ -4985,7 +4985,7 @@
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O70" s="1" t="n">
@@ -5052,7 +5052,7 @@
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O71" s="1" t="n">
@@ -5115,7 +5115,7 @@
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O72" s="1" t="n">
@@ -5182,7 +5182,7 @@
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O73" s="1" t="n">
@@ -5245,7 +5245,7 @@
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O74" s="1" t="n">
@@ -5308,7 +5308,7 @@
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O75" s="1" t="n">
@@ -5371,7 +5371,7 @@
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O76" s="1" t="n">
@@ -5434,7 +5434,7 @@
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O77" s="1" t="n">
@@ -5497,7 +5497,7 @@
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O78" s="1" t="n">
@@ -5564,7 +5564,7 @@
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O79" s="1" t="n">
@@ -5627,7 +5627,7 @@
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O80" s="1" t="n">
@@ -5690,7 +5690,7 @@
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O81" s="1" t="n">
@@ -5753,7 +5753,7 @@
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O82" s="1" t="n">
@@ -5816,7 +5816,7 @@
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O83" s="1" t="n">
@@ -5879,7 +5879,7 @@
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O84" s="1" t="n">
@@ -5942,7 +5942,7 @@
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O85" s="1" t="n">
@@ -6009,7 +6009,7 @@
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O86" s="1" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O87" s="1" t="n">
@@ -6135,7 +6135,7 @@
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O88" s="1" t="n">
@@ -6198,7 +6198,7 @@
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O89" s="1" t="n">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O90" s="1" t="n">
@@ -6324,7 +6324,7 @@
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O91" s="1" t="n">
@@ -6387,7 +6387,7 @@
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O92" s="1" t="n">
@@ -6450,7 +6450,7 @@
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O93" s="1" t="n">
@@ -6513,7 +6513,7 @@
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O94" s="1" t="n">
@@ -6576,7 +6576,7 @@
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O95" s="1" t="n">
@@ -6639,7 +6639,7 @@
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O96" s="1" t="n">
@@ -6702,7 +6702,7 @@
       </c>
       <c r="N97" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O97" s="1" t="n">
@@ -6765,7 +6765,7 @@
       </c>
       <c r="N98" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O98" s="1" t="n">
@@ -6828,7 +6828,7 @@
       </c>
       <c r="N99" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O99" s="1" t="n">
@@ -6891,7 +6891,7 @@
       </c>
       <c r="N100" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O100" s="1" t="n">
@@ -6958,7 +6958,7 @@
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O101" s="1" t="n">
@@ -7021,7 +7021,7 @@
       </c>
       <c r="N102" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O102" s="1" t="n">
@@ -7084,7 +7084,7 @@
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O103" s="1" t="n">
@@ -7151,7 +7151,7 @@
       </c>
       <c r="N104" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O104" s="1" t="n">
@@ -7214,7 +7214,7 @@
       </c>
       <c r="N105" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O105" s="1" t="n">
@@ -7277,7 +7277,7 @@
       </c>
       <c r="N106" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O106" s="1" t="n">
@@ -7340,7 +7340,7 @@
       </c>
       <c r="N107" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O107" s="1" t="n">
@@ -7407,7 +7407,7 @@
       </c>
       <c r="N108" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O108" s="1" t="n">
@@ -7470,7 +7470,7 @@
       </c>
       <c r="N109" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O109" s="1" t="n">
@@ -7533,7 +7533,7 @@
       </c>
       <c r="N110" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O110" s="1" t="n">
@@ -7596,7 +7596,7 @@
       </c>
       <c r="N111" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O111" s="1" t="n">
@@ -7659,7 +7659,7 @@
       </c>
       <c r="N112" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O112" s="1" t="n">
@@ -7722,7 +7722,7 @@
       </c>
       <c r="N113" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O113" s="1" t="n">
@@ -7785,7 +7785,7 @@
       </c>
       <c r="N114" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O114" s="1" t="n">
@@ -7852,7 +7852,7 @@
       </c>
       <c r="N115" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O115" s="1" t="n">
@@ -7915,7 +7915,7 @@
       </c>
       <c r="N116" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O116" s="1" t="n">
@@ -7978,7 +7978,7 @@
       </c>
       <c r="N117" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O117" s="1" t="n">
@@ -8041,7 +8041,7 @@
       </c>
       <c r="N118" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O118" s="1" t="n">
@@ -8104,7 +8104,7 @@
       </c>
       <c r="N119" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O119" s="1" t="n">
@@ -8167,7 +8167,7 @@
       </c>
       <c r="N120" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O120" s="1" t="n">
@@ -8230,7 +8230,7 @@
       </c>
       <c r="N121" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O121" s="1" t="n">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="N122" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O122" s="1" t="n">
@@ -8356,7 +8356,7 @@
       </c>
       <c r="N123" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O123" s="1" t="n">
@@ -8419,7 +8419,7 @@
       </c>
       <c r="N124" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O124" s="1" t="n">
@@ -8482,7 +8482,7 @@
       </c>
       <c r="N125" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O125" s="1" t="n">
@@ -8545,7 +8545,7 @@
       </c>
       <c r="N126" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O126" s="1" t="n">
@@ -8608,7 +8608,7 @@
       </c>
       <c r="N127" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O127" s="1" t="n">
@@ -8671,7 +8671,7 @@
       </c>
       <c r="N128" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O128" s="1" t="n">
@@ -8734,7 +8734,7 @@
       </c>
       <c r="N129" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O129" s="1" t="n">
@@ -8797,7 +8797,7 @@
       </c>
       <c r="N130" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O130" s="1" t="n">
@@ -8860,7 +8860,7 @@
       </c>
       <c r="N131" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O131" s="1" t="n">
@@ -8923,7 +8923,7 @@
       </c>
       <c r="N132" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O132" s="1" t="n">
@@ -8986,7 +8986,7 @@
       </c>
       <c r="N133" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O133" s="1" t="n">
@@ -9053,7 +9053,7 @@
       </c>
       <c r="N134" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O134" s="1" t="n">
@@ -9116,7 +9116,7 @@
       </c>
       <c r="N135" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O135" s="1" t="n">
@@ -9183,7 +9183,7 @@
       </c>
       <c r="N136" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O136" s="1" t="n">
@@ -9246,7 +9246,7 @@
       </c>
       <c r="N137" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O137" s="1" t="n">
@@ -9309,7 +9309,7 @@
       </c>
       <c r="N138" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O138" s="1" t="n">
@@ -9372,7 +9372,7 @@
       </c>
       <c r="N139" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O139" s="1" t="n">
@@ -9439,7 +9439,7 @@
       </c>
       <c r="N140" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O140" s="1" t="n">
@@ -9502,7 +9502,7 @@
       </c>
       <c r="N141" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O141" s="1" t="n">
@@ -9565,7 +9565,7 @@
       </c>
       <c r="N142" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O142" s="1" t="n">
@@ -9628,7 +9628,7 @@
       </c>
       <c r="N143" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O143" s="1" t="n">
@@ -9691,7 +9691,7 @@
       </c>
       <c r="N144" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O144" s="1" t="n">
@@ -9754,7 +9754,7 @@
       </c>
       <c r="N145" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O145" s="1" t="n">
@@ -9817,7 +9817,7 @@
       </c>
       <c r="N146" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O146" s="1" t="n">
@@ -9880,7 +9880,7 @@
       </c>
       <c r="N147" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O147" s="1" t="n">
@@ -9943,7 +9943,7 @@
       </c>
       <c r="N148" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O148" s="1" t="n">
@@ -10006,7 +10006,7 @@
       </c>
       <c r="N149" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O149" s="1" t="n">
@@ -10069,7 +10069,7 @@
       </c>
       <c r="N150" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O150" s="1" t="n">
@@ -10132,7 +10132,7 @@
       </c>
       <c r="N151" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O151" s="1" t="n">
@@ -10195,7 +10195,7 @@
       </c>
       <c r="N152" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O152" s="1" t="n">
@@ -10258,7 +10258,7 @@
       </c>
       <c r="N153" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O153" s="1" t="n">
@@ -10321,7 +10321,7 @@
       </c>
       <c r="N154" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O154" s="1" t="n">
@@ -10384,7 +10384,7 @@
       </c>
       <c r="N155" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O155" s="1" t="n">
@@ -10447,7 +10447,7 @@
       </c>
       <c r="N156" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O156" s="1" t="n">
@@ -10510,7 +10510,7 @@
       </c>
       <c r="N157" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O157" s="1" t="n">
@@ -10573,7 +10573,7 @@
       </c>
       <c r="N158" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O158" s="1" t="n">
@@ -10636,7 +10636,7 @@
       </c>
       <c r="N159" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O159" s="1" t="n">
@@ -10699,7 +10699,7 @@
       </c>
       <c r="N160" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O160" s="1" t="n">
@@ -10762,7 +10762,7 @@
       </c>
       <c r="N161" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O161" s="1" t="n">
@@ -10825,7 +10825,7 @@
       </c>
       <c r="N162" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O162" s="1" t="n">
@@ -10888,7 +10888,7 @@
       </c>
       <c r="N163" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O163" s="1" t="n">
@@ -10951,7 +10951,7 @@
       </c>
       <c r="N164" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O164" s="1" t="n">
@@ -11014,7 +11014,7 @@
       </c>
       <c r="N165" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O165" s="1" t="n">
@@ -11077,7 +11077,7 @@
       </c>
       <c r="N166" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O166" s="1" t="n">
@@ -11140,7 +11140,7 @@
       </c>
       <c r="N167" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O167" s="1" t="n">
@@ -11203,7 +11203,7 @@
       </c>
       <c r="N168" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O168" s="1" t="n">
@@ -11266,7 +11266,7 @@
       </c>
       <c r="N169" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O169" s="1" t="n">
@@ -11329,7 +11329,7 @@
       </c>
       <c r="N170" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O170" s="1" t="n">
@@ -11392,7 +11392,7 @@
       </c>
       <c r="N171" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O171" s="1" t="n">
@@ -11455,7 +11455,7 @@
       </c>
       <c r="N172" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O172" s="1" t="n">
@@ -11518,7 +11518,7 @@
       </c>
       <c r="N173" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O173" s="1" t="n">
@@ -11581,7 +11581,7 @@
       </c>
       <c r="N174" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O174" s="1" t="n">
@@ -11644,7 +11644,7 @@
       </c>
       <c r="N175" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O175" s="1" t="n">
@@ -11707,7 +11707,7 @@
       </c>
       <c r="N176" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O176" s="1" t="n">
@@ -11770,7 +11770,7 @@
       </c>
       <c r="N177" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O177" s="1" t="n">
@@ -11833,7 +11833,7 @@
       </c>
       <c r="N178" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O178" s="1" t="n">
@@ -11896,7 +11896,7 @@
       </c>
       <c r="N179" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O179" s="1" t="n">
@@ -11959,7 +11959,7 @@
       </c>
       <c r="N180" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O180" s="1" t="n">
@@ -12022,7 +12022,7 @@
       </c>
       <c r="N181" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O181" s="1" t="n">
@@ -12085,7 +12085,7 @@
       </c>
       <c r="N182" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O182" s="1" t="n">
@@ -12148,7 +12148,7 @@
       </c>
       <c r="N183" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O183" s="1" t="n">
@@ -12211,7 +12211,7 @@
       </c>
       <c r="N184" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O184" s="1" t="n">
@@ -12274,7 +12274,7 @@
       </c>
       <c r="N185" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O185" s="1" t="n">
@@ -12337,7 +12337,7 @@
       </c>
       <c r="N186" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O186" s="1" t="n">
@@ -12400,7 +12400,7 @@
       </c>
       <c r="N187" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O187" s="1" t="n">
@@ -12463,7 +12463,7 @@
       </c>
       <c r="N188" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O188" s="1" t="n">
@@ -12526,7 +12526,7 @@
       </c>
       <c r="N189" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O189" s="1" t="n">
@@ -12589,7 +12589,7 @@
       </c>
       <c r="N190" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O190" s="1" t="n">
@@ -12652,7 +12652,7 @@
       </c>
       <c r="N191" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O191" s="1" t="n">
@@ -12715,7 +12715,7 @@
       </c>
       <c r="N192" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O192" s="1" t="n">
@@ -12778,7 +12778,7 @@
       </c>
       <c r="N193" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O193" s="1" t="n">
@@ -12841,7 +12841,7 @@
       </c>
       <c r="N194" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O194" s="1" t="n">
@@ -12904,7 +12904,7 @@
       </c>
       <c r="N195" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O195" s="1" t="n">
@@ -12967,7 +12967,7 @@
       </c>
       <c r="N196" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O196" s="1" t="n">
@@ -13030,7 +13030,7 @@
       </c>
       <c r="N197" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O197" s="1" t="n">
@@ -13093,7 +13093,7 @@
       </c>
       <c r="N198" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O198" s="1" t="n">
@@ -13156,7 +13156,7 @@
       </c>
       <c r="N199" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O199" s="1" t="n">
@@ -13219,7 +13219,7 @@
       </c>
       <c r="N200" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O200" s="1" t="n">
@@ -13282,7 +13282,7 @@
       </c>
       <c r="N201" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O201" s="1" t="n">
@@ -13345,7 +13345,7 @@
       </c>
       <c r="N202" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:14</t>
+          <t>2026-10-27 14:50:51</t>
         </is>
       </c>
       <c r="O202" s="1" t="n">
